--- a/data/Country_Summary.xlsx
+++ b/data/Country_Summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,27 +436,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>GY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3339260</v>
+        <v>62003028</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>429590</v>
+        <v>1669630</v>
       </c>
     </row>
     <row r="4">
@@ -466,33 +466,33 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>100000</v>
+        <v>1271032</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>429590</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>VN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -501,7 +501,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>UG</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -514,11 +514,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -527,11 +527,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -553,11 +553,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -579,11 +579,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -592,7 +592,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -605,13 +605,91 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BT</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>BF</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
         <v>0</v>
       </c>
     </row>
